--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="485">
   <si>
     <t>Filename</t>
   </si>
@@ -808,676 +808,667 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9983,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0102,0.0001,0.0001,0.9983</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0564,0.0001,0.0000,0.9942</t>
+  </si>
+  <si>
+    <t>0.9972,0.0000,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.0023,0.0003,0.0000,0.9996</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.0039,0.9864,0.0006</t>
+  </si>
+  <si>
+    <t>0.0059,0.0036,0.9916,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.9955,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0007,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0251,0.9755,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8650,0.0008,0.1522,0.0002</t>
+  </si>
+  <si>
+    <t>0.9785,0.0004,0.0181,0.0000</t>
+  </si>
+  <si>
+    <t>0.0087,0.0006,0.9906,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0005,0.9904,0.0003</t>
+  </si>
+  <si>
+    <t>0.0060,0.0002,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.3357,0.7415,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.8498,0.0975,0.0105,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9947,0.0321,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.7454,0.0007,0.3961,0.0002</t>
+  </si>
+  <si>
+    <t>0.7812,0.2601,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9974,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0061,0.8284,0.2176,0.0454</t>
+  </si>
+  <si>
+    <t>0.0038,0.0025,0.9902,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0025,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0525,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9980,0.0075,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0048,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0282,0.0109,0.0003,0.9756</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.0826,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0389,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8944,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9999,0.0010</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0014,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9808,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0178,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0028,0.9980,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0282,0.9661,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9696,0.0007,0.0305,0.0002</t>
+  </si>
+  <si>
+    <t>0.9074,0.0113,0.0510,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0029,0.9997,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9930,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0593,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9841,0.9946,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.0015,0.9971</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0054,0.0001,0.0009,0.9964</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.9940,0.4581,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9875,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9794,0.9833,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9841,0.8998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9669,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0101,0.0023,0.9882,0.0002</t>
+  </si>
+  <si>
+    <t>0.9918,0.0003,0.0044,0.0000</t>
+  </si>
+  <si>
+    <t>0.0394,0.0006,0.9741,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9984,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0417,0.9549,0.0054,0.0002</t>
+  </si>
+  <si>
+    <t>0.5328,0.0204,0.3005,0.0013</t>
+  </si>
+  <si>
+    <t>0.0064,0.0008,0.9883,0.0009</t>
+  </si>
+  <si>
+    <t>0.0582,0.8776,0.0282,0.0017</t>
+  </si>
+  <si>
+    <t>0.0042,0.0019,0.9919,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0023,0.0108,0.9857</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9810,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9962,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.8513,0.1816,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.9750,0.0202,0.0025,0.0002</t>
+  </si>
+  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9720,0.0004,0.0278,0.0000</t>
-  </si>
-  <si>
-    <t>0.1062,0.0019,0.8807,0.0011</t>
-  </si>
-  <si>
-    <t>0.0089,0.0009,0.9916,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.0001,0.9894,0.0002</t>
-  </si>
-  <si>
-    <t>0.9226,0.0015,0.0764,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9983,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0147,0.9777,0.0038,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4589,0.0009,0.6106,0.0003</t>
-  </si>
-  <si>
-    <t>0.9359,0.0005,0.0838,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0001,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9007,0.1297,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.8038,0.0873,0.0462,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9699,0.4334,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8725,0.0004,0.1878,0.0002</t>
-  </si>
-  <si>
-    <t>0.9881,0.0112,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.9922,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0101,0.5552,0.4588,0.0276</t>
-  </si>
-  <si>
-    <t>0.0042,0.0030,0.9885,0.0008</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.0001,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.2144,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0150,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0169,0.0140,0.0004,0.9807</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0313,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0139,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0009,0.9943,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.0001,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0016,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0035,0.9999,0.0017</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9884,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0086,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0021,0.9929,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9918,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9993,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0003,0.0053,0.0000</t>
-  </si>
-  <si>
-    <t>0.3842,0.0023,0.6589,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0052,0.9994,0.0032</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9726,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9937,0.9886,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.1774,0.9760</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0088,0.0002,0.0000,0.9984</t>
-  </si>
-  <si>
-    <t>0.0065,0.0001,0.0005,0.9963</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0036,0.9974</t>
-  </si>
-  <si>
-    <t>0.0025,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.0722,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9929,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.2684,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9906,0.5505,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9937,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0129,0.0008,0.9889,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0008,0.9953,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.9935,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.0083,0.9900,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6346,0.4556,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.3888,0.0109,0.5116,0.0020</t>
-  </si>
-  <si>
-    <t>0.0655,0.0011,0.9359,0.0005</t>
-  </si>
-  <si>
-    <t>0.1619,0.0277,0.7207,0.0007</t>
-  </si>
-  <si>
-    <t>0.0060,0.0018,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0026,0.0008,0.9984</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9885,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.9954,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.4178,0.6327,0.0090,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0084,0.0054,0.0007</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0002,0.0003</t>
+    <t>0.9992,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.7120,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4235,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1415,0.0098,0.7621,0.0231</t>
+  </si>
+  <si>
+    <t>0.3639,0.0002,0.7537,0.0002</t>
+  </si>
+  <si>
+    <t>0.9803,0.0008,0.0112,0.0001</t>
+  </si>
+  <si>
+    <t>0.3211,0.0001,0.0004,0.8486</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.1951,0.8149,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9302,0.0697,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.8058,0.0001,0.0002,0.4673</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0345,0.9975,0.0008</t>
+  </si>
+  <si>
+    <t>0.9950,0.0001,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0000,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.8234,0.2625,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0773,0.8731,0.0143,0.0030</t>
+  </si>
+  <si>
+    <t>0.9727,0.0047,0.0088,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0027,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9881,0.0115,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9233,0.0776,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.3340,0.6522,0.0164,0.0006</t>
+  </si>
+  <si>
+    <t>0.9751,0.0175,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0053,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9816,0.0129,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0365,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9911,0.0031,0.0029,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.0190,0.9895,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0054,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0042,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0024,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0009,0.9954,0.0002</t>
+  </si>
+  <si>
+    <t>0.9818,0.0009,0.0090,0.0001</t>
+  </si>
+  <si>
+    <t>0.0336,0.6045,0.3091,0.0012</t>
+  </si>
+  <si>
+    <t>0.0333,0.5442,0.4389,0.0002</t>
+  </si>
+  <si>
+    <t>0.5535,0.0085,0.4095,0.0001</t>
+  </si>
+  <si>
+    <t>0.9420,0.0030,0.0224,0.0023</t>
+  </si>
+  <si>
+    <t>0.0126,0.0012,0.9779,0.0052</t>
+  </si>
+  <si>
+    <t>0.9871,0.0136,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9968,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.1108,0.9188,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.3952,0.7222,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0257,0.9757,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.8574,0.0076,0.0843,0.0003</t>
+  </si>
+  <si>
+    <t>0.9839,0.0011,0.0077,0.0001</t>
+  </si>
+  <si>
+    <t>0.6951,0.0011,0.2614,0.0016</t>
+  </si>
+  <si>
+    <t>0.3450,0.0039,0.7325,0.0000</t>
+  </si>
+  <si>
+    <t>0.9356,0.0002,0.0755,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0146,0.9954,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0943,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0308,0.0007,0.9772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0804,0.9739,0.0009</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9996,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8428,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9351,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1876,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0010,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9626,0.0029,0.0179,0.0008</t>
-  </si>
-  <si>
-    <t>0.0411,0.0001,0.9831,0.0000</t>
-  </si>
-  <si>
-    <t>0.3788,0.0042,0.5908,0.0011</t>
-  </si>
-  <si>
-    <t>0.1932,0.0000,0.0001,0.9602</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0003,0.9998</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.0012,0.9982</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9907,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.2189,0.7881,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9921,0.0001,0.0001,0.0053</t>
-  </si>
-  <si>
-    <t>0.0004,0.0417,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.9881,0.0002,0.0056,0.0018</t>
-  </si>
-  <si>
-    <t>0.9777,0.0000,0.0009,0.0100</t>
-  </si>
-  <si>
-    <t>0.8111,0.2121,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8225,0.1005,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.9801,0.0022,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0011,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9573,0.0674,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9735,0.0278,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0593,0.9196,0.0168,0.0006</t>
-  </si>
-  <si>
-    <t>0.8301,0.1260,0.0267,0.0008</t>
-  </si>
-  <si>
-    <t>0.9888,0.0139,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0003,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9950,0.0017,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9798,0.0167,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0502,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9557,0.0161,0.0208,0.0021</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0021,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.0135,0.9942,0.0002</t>
+    <t>0.0002,0.0287,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.7964,0.6759,0.0002</t>
+  </si>
+  <si>
+    <t>0.8083,0.0016,0.1851,0.0023</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.4373,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0024,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.3575,0.0013,0.6604,0.0006</t>
+  </si>
+  <si>
+    <t>0.9791,0.0004,0.0171,0.0001</t>
+  </si>
+  <si>
+    <t>0.9195,0.0000,0.1350,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0036,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0024,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9985,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0005,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0033,0.9919,0.0004</t>
-  </si>
-  <si>
-    <t>0.0086,0.0005,0.9923,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0013,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.1608,0.0277,0.7467,0.0002</t>
-  </si>
-  <si>
-    <t>0.0995,0.7728,0.0495,0.0004</t>
-  </si>
-  <si>
-    <t>0.0701,0.0039,0.9360,0.0000</t>
-  </si>
-  <si>
-    <t>0.9313,0.0113,0.0205,0.0007</t>
-  </si>
-  <si>
-    <t>0.0389,0.0067,0.9333,0.0028</t>
-  </si>
-  <si>
-    <t>0.3781,0.7231,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9972,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.2906,0.7904,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9333,0.1244,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0625,0.9594,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9842,0.0017,0.0043,0.0000</t>
-  </si>
-  <si>
-    <t>0.9884,0.0003,0.0078,0.0000</t>
-  </si>
-  <si>
-    <t>0.9950,0.0001,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.7550,0.0011,0.3328,0.0001</t>
-  </si>
-  <si>
-    <t>0.7169,0.0003,0.3369,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0116,0.0114,0.9793,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.0050,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0019,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0716,0.9811,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0012,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0039,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0224,0.0635,0.9304,0.0006</t>
-  </si>
-  <si>
-    <t>0.8858,0.0007,0.0985,0.0022</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.2123,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0092,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0010,0.9930,0.0004</t>
-  </si>
-  <si>
-    <t>0.9299,0.0074,0.0367,0.0002</t>
-  </si>
-  <si>
-    <t>0.9814,0.0002,0.0179,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0001,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0057,0.9875,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0144,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.0075,0.9818,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0379,0.0003,0.9408,0.0082</t>
-  </si>
-  <si>
-    <t>0.0088,0.0002,0.9927,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.9800,0.0001,0.0002,0.0207</t>
-  </si>
-  <si>
-    <t>0.0270,0.0011,0.0001,0.9934</t>
-  </si>
-  <si>
-    <t>0.3554,0.0003,0.0001,0.8607</t>
-  </si>
-  <si>
-    <t>0.9429,0.0004,0.0050,0.0194</t>
+    <t>0.0011,0.0290,0.9917,0.0004</t>
+  </si>
+  <si>
+    <t>0.0099,0.0314,0.9597,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.3590,0.0003,0.6473,0.0026</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0000,0.0000,0.0441</t>
+  </si>
+  <si>
+    <t>0.0187,0.0005,0.0000,0.9950</t>
+  </si>
+  <si>
+    <t>0.3496,0.0000,0.0009,0.7976</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.6623,0.0005,0.0007,0.5538</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1854,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1877,7 +1868,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1891,7 +1882,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1905,7 +1896,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1919,7 +1910,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1933,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1947,7 +1938,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1961,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1975,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1989,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2003,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2031,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,7 +2036,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,7 +2050,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2073,7 +2064,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2087,7 +2078,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2101,7 +2092,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2115,7 +2106,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2129,7 +2120,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2143,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2157,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2168,10 +2159,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,7 +2176,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2199,7 +2190,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,7 +2204,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2227,7 +2218,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2241,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2255,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2266,10 +2257,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,7 +2274,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2297,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2311,7 +2302,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2325,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2339,7 +2330,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2353,7 +2344,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2367,7 +2358,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2381,7 +2372,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2395,7 +2386,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2409,7 +2400,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2423,7 +2414,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2437,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,7 +2442,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2465,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2479,7 +2470,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2493,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2507,7 +2498,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2521,7 +2512,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2535,7 +2526,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,10 +2537,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2563,7 +2554,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2577,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2591,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2605,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2619,7 +2610,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2633,7 +2624,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2647,7 +2638,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2661,7 +2652,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2675,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2689,7 +2680,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>270</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2703,7 +2694,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2717,7 +2708,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2731,7 +2722,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2745,7 +2736,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2759,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2773,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2787,7 +2778,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2801,7 +2792,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2815,7 +2806,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2826,10 +2817,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2843,7 +2834,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2857,7 +2848,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2871,7 +2862,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2885,7 +2876,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2899,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2913,7 +2904,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,7 +2918,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2941,7 +2932,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2955,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2969,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2983,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2997,7 +2988,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3011,7 +3002,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3025,7 +3016,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3036,10 +3027,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3053,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3067,7 +3058,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3081,7 +3072,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3095,7 +3086,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3123,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3137,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3151,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3165,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3179,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3193,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3207,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3221,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3249,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3263,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3277,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3291,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3305,7 +3296,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3319,7 +3310,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3333,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3347,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3361,7 +3352,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3375,7 +3366,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3389,7 +3380,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3403,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3417,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3431,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3442,10 +3433,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3456,10 +3447,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3473,7 +3464,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,10 +3475,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,7 +3492,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3515,7 +3506,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3529,7 +3520,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3543,7 +3534,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>310</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3557,7 +3548,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3571,7 +3562,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3585,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3596,10 +3587,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3613,7 +3604,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3627,7 +3618,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>272</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3641,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3655,7 +3646,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3669,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3683,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>268</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3697,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3711,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3725,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>269</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3739,7 +3730,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3750,10 +3741,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3767,7 +3758,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3781,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3795,7 +3786,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3806,10 +3797,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3834,10 +3825,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3851,7 +3842,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3865,7 +3856,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3879,7 +3870,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3893,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3907,7 +3898,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3921,7 +3912,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3935,7 +3926,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3949,7 +3940,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3960,10 +3951,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3977,7 +3968,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3991,7 +3982,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4005,7 +3996,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4019,7 +4010,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,7 +4024,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4047,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,7 +4052,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4075,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4089,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4100,10 +4091,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4117,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4131,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4145,7 +4136,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4159,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4173,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4187,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>269</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4201,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4215,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4229,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4243,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4257,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4271,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4285,7 +4276,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4299,7 +4290,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4313,7 +4304,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4327,7 +4318,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4341,7 +4332,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4369,7 +4360,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4383,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4397,7 +4388,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4411,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4425,7 +4416,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4453,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4467,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>430</v>
+        <v>327</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4481,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4509,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,10 +4511,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4534,10 +4525,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4551,7 +4542,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4562,10 +4553,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,7 +4570,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4593,7 +4584,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4604,10 +4595,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4621,7 +4612,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,7 +4626,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,10 +4637,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4663,7 +4654,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4677,7 +4668,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4691,7 +4682,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4705,7 +4696,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4716,10 +4707,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4747,7 +4738,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4761,7 +4752,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,7 +4766,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4789,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4803,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4817,7 +4808,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4831,7 +4822,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4845,7 +4836,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4859,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4873,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4887,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4901,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4915,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>272</v>
+        <v>455</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4929,7 +4920,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,10 +4931,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4957,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4971,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>462</v>
+        <v>291</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4985,7 +4976,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,7 +4990,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5013,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5027,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5041,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5055,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5069,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5083,7 +5074,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,7 +5088,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5111,7 +5102,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>377</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5125,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5139,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5153,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>347</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5167,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5181,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>475</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5195,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5209,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>272</v>
+        <v>321</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5223,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>272</v>
+        <v>471</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5237,7 +5228,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5251,7 +5242,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,7 +5256,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5279,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5293,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5335,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5349,7 +5340,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5363,7 +5354,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5377,7 +5368,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5391,7 +5382,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5405,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5416,10 +5407,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
